--- a/diseases/d055/2026-2029.xlsx
+++ b/diseases/d055/2026-2029.xlsx
@@ -1729,6 +1729,154 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>clonorchiasis</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>12759</v>
+      </c>
+      <c r="O9" t="n">
+        <v>12759</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.9030273039138147</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>cdc_weekly</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>China CDC Weekly</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>cdc_weekly; nhc; pubmed</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>web; web; web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1762,7 +1910,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -1845,7 +1993,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -1855,7 +2003,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -1907,7 +2055,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>72347</v>
+        <v>85106</v>
       </c>
     </row>
     <row r="16">
@@ -1917,7 +2065,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">

--- a/diseases/d055/2026-2029.xlsx
+++ b/diseases/d055/2026-2029.xlsx
@@ -1609,12 +1609,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1639,93 +1639,101 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>12460</v>
+        <v>6</v>
       </c>
       <c r="O8" t="n">
-        <v>12460</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.8818653661545678</v>
+        <v>6</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -1752,128 +1760,2850 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>CN-JS</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Jiangsu, China</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>6</v>
+      </c>
+      <c r="O9" t="n">
+        <v>6</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>country:CN-JS:national</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Human Clonorchis sinensis infection. The Chinese source category 肝吸虫病 denotes clonorchiasis, not all trematode infections.</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AT9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>clonorchiasis</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>CN-SH</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Shanghai, China</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>5</v>
+      </c>
+      <c r="O10" t="n">
+        <v>5</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AT10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>clonorchiasis</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>CN-SH</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Shanghai, China</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>5</v>
+      </c>
+      <c r="O11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>country:CN-SH:national</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Human Clonorchis sinensis infection. The Chinese source category 肝吸虫病 denotes clonorchiasis, not all trematode infections.</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AT11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>clonorchiasis</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>D055</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>Clonorchiasis</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>肝吸虫病</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>Parasitic</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>12460</v>
+      </c>
+      <c r="O12" t="n">
+        <v>12460</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.8818653661545678</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>cdc_weekly</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>China CDC Weekly</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>cdc_weekly; nhc; pubmed</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>web; web; web</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>clonorchiasis</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>CN-FJ</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Fujian, China</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>7</v>
+      </c>
+      <c r="O13" t="n">
+        <v>7</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AT13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.fujian.gov.cn/xxgk/zfxxgkzl/zfxxgkml/ggws/fdcrbyqgb/</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>clonorchiasis</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>CN-FJ</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Fujian, China</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>7</v>
+      </c>
+      <c r="O14" t="n">
+        <v>7</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>country:CN-FJ:national</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Human Clonorchis sinensis infection. The Chinese source category 肝吸虫病 denotes clonorchiasis, not all trematode infections.</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AT14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.fujian.gov.cn/xxgk/zfxxgkzl/zfxxgkml/ggws/fdcrbyqgb/</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>clonorchiasis</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>CN-JS</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Jiangsu, China</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>8</v>
+      </c>
+      <c r="O15" t="n">
+        <v>8</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AT15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>clonorchiasis</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>CN-JS</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Jiangsu, China</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>8</v>
+      </c>
+      <c r="O16" t="n">
+        <v>8</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>country:CN-JS:national</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Human Clonorchis sinensis infection. The Chinese source category 肝吸虫病 denotes clonorchiasis, not all trematode infections.</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AT16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>clonorchiasis</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>CN-SH</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Shanghai, China</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>10</v>
+      </c>
+      <c r="O17" t="n">
+        <v>10</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AT17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>clonorchiasis</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>CN-SH</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Shanghai, China</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>10</v>
+      </c>
+      <c r="O18" t="n">
+        <v>10</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>country:CN-SH:national</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Human Clonorchis sinensis infection. The Chinese source category 肝吸虫病 denotes clonorchiasis, not all trematode infections.</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AT18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>clonorchiasis</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="N9" t="n">
+      <c r="N19" t="n">
         <v>12759</v>
       </c>
-      <c r="O9" t="n">
+      <c r="O19" t="n">
         <v>12759</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q19" t="n">
         <v>1</v>
       </c>
-      <c r="R9" t="n">
+      <c r="R19" t="n">
         <v>0.9030273039138147</v>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
+      <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP9" t="inlineStr">
+      <c r="AP19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR9" t="inlineStr">
+      <c r="AR19" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS9" t="inlineStr"/>
-      <c r="AT9" t="n">
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="n">
         <v>0</v>
       </c>
-      <c r="AU9" t="inlineStr">
+      <c r="AU19" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV9" t="inlineStr">
+      <c r="AV19" t="inlineStr">
         <is>
           <t>cdc_weekly</t>
         </is>
       </c>
-      <c r="AW9" t="inlineStr">
+      <c r="AW19" t="inlineStr">
         <is>
           <t>China CDC Weekly</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX19" t="inlineStr">
         <is>
           <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr">
+      <c r="AY19" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
+      <c r="AZ19" t="inlineStr">
         <is>
           <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
-      <c r="BA9" t="inlineStr">
+      <c r="BA19" t="inlineStr">
         <is>
           <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
-      <c r="BB9" t="inlineStr">
+      <c r="BB19" t="inlineStr">
         <is>
           <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
-      <c r="BC9" t="inlineStr">
+      <c r="BC19" t="inlineStr">
         <is>
           <t>web; web; web</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>clonorchiasis</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>CN-JS</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Jiangsu, China</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>3</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AT20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>clonorchiasis</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>CN-JS</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Jiangsu, China</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>3</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>country:CN-JS:national</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Human Clonorchis sinensis infection. The Chinese source category 肝吸虫病 denotes clonorchiasis, not all trematode infections.</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AT21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>clonorchiasis</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>CN-SH</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Shanghai, China</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>11</v>
+      </c>
+      <c r="O22" t="n">
+        <v>11</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AT22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+        </is>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>clonorchiasis</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>CN-SH</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Shanghai, China</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>11</v>
+      </c>
+      <c r="O23" t="n">
+        <v>11</v>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>country:CN-SH:national</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Human Clonorchis sinensis infection. The Chinese source category 肝吸虫病 denotes clonorchiasis, not all trematode infections.</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN23" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AT23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+        </is>
+      </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -1993,7 +4723,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
@@ -2003,7 +4733,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11">
@@ -2023,7 +4753,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -2033,7 +4763,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -2055,7 +4785,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>85106</v>
+        <v>85156</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d055/2026-2029.xlsx
+++ b/diseases/d055/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -924,6 +929,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1072,6 +1082,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1220,6 +1235,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1368,6 +1388,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1516,6 +1541,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2444,6 +2474,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3760,6 +3795,11 @@
       <c r="S19" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">

--- a/diseases/d055/2026-2029.xlsx
+++ b/diseases/d055/2026-2029.xlsx
@@ -1180,12 +1180,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CN-SX</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Shanxi, China</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1210,29 +1210,28 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>10761</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>10761</v>
-      </c>
-      <c r="Q5" t="n">
         <v>0</v>
       </c>
-      <c r="R5" t="n">
-        <v>0.7616174321981786</v>
-      </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1242,66 +1241,70 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.shanxi.gov.cn/zfxxgk/fdzdgknr/yqfb/</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -1328,17 +1331,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CN-SX</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Shanxi, China</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1363,29 +1366,48 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>11219</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>11219</v>
-      </c>
-      <c r="Q6" t="n">
         <v>0</v>
       </c>
-      <c r="R6" t="n">
-        <v>0.794032708096958</v>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1393,68 +1415,130 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>country:CN-SX:national</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Human Clonorchis sinensis infection. The Chinese source category 肝吸虫病 denotes clonorchiasis, not all trematode infections.</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN6" t="b">
+        <v>1</v>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.shanxi.gov.cn/zfxxgk/fdzdgknr/yqfb/</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -1516,25 +1600,25 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>11573</v>
+        <v>10761</v>
       </c>
       <c r="O7" t="n">
-        <v>11573</v>
+        <v>10761</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8190873099925211</v>
+        <v>0.7616174321981786</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1639,12 +1723,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-SX</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Shanxi, China</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1669,19 +1753,19 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1758,7 +1842,7 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.shanxi.gov.cn/zfxxgk/fdzdgknr/yqfb/</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -1795,12 +1879,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-SX</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Shanxi, China</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1825,19 +1909,19 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1881,7 +1965,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>country:CN-JS:national</t>
+          <t>country:CN-SX:national</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -1992,7 +2076,7 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.shanxi.gov.cn/zfxxgk/fdzdgknr/yqfb/</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -2029,12 +2113,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -2059,28 +2143,29 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>5</v>
+        <v>11219</v>
       </c>
       <c r="O10" t="n">
-        <v>5</v>
+        <v>11219</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.794032708096958</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -2090,70 +2175,66 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>cn_province_datacenter</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>cn_province_datacenter; cn_province_monthly_report</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -2180,17 +2261,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-GX</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Guangxi, China</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -2215,112 +2296,34 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>2933</v>
       </c>
       <c r="O11" t="n">
-        <v>5</v>
+        <v>2933</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
           <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>肝吸虫病</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>provincial_statutory_infectious_disease_monthly_report</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>country:CN-SH:national</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Human Clonorchis sinensis infection. The Chinese source category 肝吸虫病 denotes clonorchiasis, not all trematode infections.</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN11" t="b">
-        <v>1</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -2382,7 +2385,7 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -2414,17 +2417,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CN-GX</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Guangxi, China</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2449,29 +2452,48 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>12460</v>
+        <v>2933</v>
       </c>
       <c r="O12" t="n">
-        <v>12460</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.8818653661545678</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>2933</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2479,68 +2501,130 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>country:CN-GX:national</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Human Clonorchis sinensis infection. The Chinese source category 肝吸虫病 denotes clonorchiasis, not all trematode infections.</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN12" t="b">
+        <v>1</v>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -2572,12 +2656,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CN-FJ</t>
+          <t>CN-JX</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fujian, China</t>
+          <t>Jiangxi, China</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2602,19 +2686,19 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O13" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -2691,7 +2775,7 @@
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.fujian.gov.cn/xxgk/zfxxgkzl/zfxxgkml/ggws/fdcrbyqgb/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.jxcdc.cn/</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
@@ -2728,12 +2812,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CN-FJ</t>
+          <t>CN-JX</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fujian, China</t>
+          <t>Jiangxi, China</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2758,19 +2842,19 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -2814,7 +2898,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>country:CN-FJ:national</t>
+          <t>country:CN-JX:national</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -2925,7 +3009,7 @@
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.fujian.gov.cn/xxgk/zfxxgkzl/zfxxgkml/ggws/fdcrbyqgb/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.jxcdc.cn/</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
@@ -2962,12 +3046,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2992,28 +3076,29 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>8</v>
+        <v>11573</v>
       </c>
       <c r="O15" t="n">
-        <v>8</v>
+        <v>11573</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.8190873099925211</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -3023,70 +3108,66 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>cn_province_datacenter</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>cn_province_datacenter; cn_province_monthly_report</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -3113,17 +3194,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-GX</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Guangxi, China</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -3148,112 +3229,34 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>8</v>
+        <v>3159</v>
       </c>
       <c r="O16" t="n">
-        <v>8</v>
+        <v>3159</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
           <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>肝吸虫病</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>provincial_statutory_infectious_disease_monthly_report</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>country:CN-JS:national</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG16" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Human Clonorchis sinensis infection. The Chinese source category 肝吸虫病 denotes clonorchiasis, not all trematode infections.</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN16" t="b">
-        <v>1</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -3315,7 +3318,7 @@
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
@@ -3347,17 +3350,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-GX</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Guangxi, China</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -3382,34 +3385,112 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>10</v>
+        <v>3159</v>
       </c>
       <c r="O17" t="n">
-        <v>10</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+        <v>3159</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
           <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
         </is>
       </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>country:CN-GX:national</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Human Clonorchis sinensis infection. The Chinese source category 肝吸虫病 denotes clonorchiasis, not all trematode infections.</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN17" t="b">
+        <v>1</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -3471,7 +3552,7 @@
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
@@ -3503,17 +3584,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -3538,112 +3619,34 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O18" t="n">
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
           <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>肝吸虫病</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>provincial_statutory_infectious_disease_monthly_report</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>country:CN-SH:national</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG18" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Human Clonorchis sinensis infection. The Chinese source category 肝吸虫病 denotes clonorchiasis, not all trematode infections.</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN18" t="b">
-        <v>1</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -3705,7 +3708,7 @@
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -3737,17 +3740,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -3772,98 +3775,179 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>12759</v>
+        <v>6</v>
       </c>
       <c r="O19" t="n">
-        <v>12759</v>
-      </c>
-      <c r="Q19" t="n">
+        <v>6</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>country:CN-JS:national</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Human Clonorchis sinensis infection. The Chinese source category 肝吸虫病 denotes clonorchiasis, not all trematode infections.</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN19" t="b">
         <v>1</v>
       </c>
-      <c r="R19" t="n">
-        <v>0.9030273039138147</v>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS19" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -3895,12 +3979,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-JX</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Jiangxi, China</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3925,19 +4009,19 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="O20" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -4014,7 +4098,7 @@
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.jxcdc.cn/</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
@@ -4051,12 +4135,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-JX</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Jiangxi, China</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -4081,19 +4165,19 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="O21" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -4137,7 +4221,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>country:CN-JS:national</t>
+          <t>country:CN-JX:national</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -4248,7 +4332,7 @@
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.jxcdc.cn/</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
@@ -4315,19 +4399,19 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="O22" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -4471,19 +4555,19 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="O23" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
@@ -4642,6 +4726,4602 @@
         </is>
       </c>
       <c r="BC23" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>clonorchiasis</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>12460</v>
+      </c>
+      <c r="O24" t="n">
+        <v>12460</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.8818653661545678</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV24" t="inlineStr">
+        <is>
+          <t>cdc_weekly</t>
+        </is>
+      </c>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>China CDC Weekly</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>cdc_weekly; nhc; pubmed</t>
+        </is>
+      </c>
+      <c r="BA24" t="inlineStr">
+        <is>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+        </is>
+      </c>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+        </is>
+      </c>
+      <c r="BC24" t="inlineStr">
+        <is>
+          <t>web; web; web</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>clonorchiasis</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>CN-FJ</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Fujian, China</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>7</v>
+      </c>
+      <c r="O25" t="n">
+        <v>7</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AT25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV25" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA25" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB25" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.fujian.gov.cn/xxgk/zfxxgkzl/zfxxgkml/ggws/fdcrbyqgb/</t>
+        </is>
+      </c>
+      <c r="BC25" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>clonorchiasis</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>CN-FJ</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Fujian, China</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>7</v>
+      </c>
+      <c r="O26" t="n">
+        <v>7</v>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>country:CN-FJ:national</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Human Clonorchis sinensis infection. The Chinese source category 肝吸虫病 denotes clonorchiasis, not all trematode infections.</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AT26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV26" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA26" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB26" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.fujian.gov.cn/xxgk/zfxxgkzl/zfxxgkml/ggws/fdcrbyqgb/</t>
+        </is>
+      </c>
+      <c r="BC26" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>clonorchiasis</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>CN-GX</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Guangxi, China</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>3395</v>
+      </c>
+      <c r="O27" t="n">
+        <v>3395</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AT27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV27" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA27" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB27" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
+        </is>
+      </c>
+      <c r="BC27" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>clonorchiasis</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>CN-GX</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Guangxi, China</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>3395</v>
+      </c>
+      <c r="O28" t="n">
+        <v>3395</v>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>country:CN-GX:national</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Human Clonorchis sinensis infection. The Chinese source category 肝吸虫病 denotes clonorchiasis, not all trematode infections.</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP28" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AT28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV28" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA28" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB28" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
+        </is>
+      </c>
+      <c r="BC28" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>clonorchiasis</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>CN-JS</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Jiangsu, China</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>8</v>
+      </c>
+      <c r="O29" t="n">
+        <v>8</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP29" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AT29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV29" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA29" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB29" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+        </is>
+      </c>
+      <c r="BC29" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>clonorchiasis</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>CN-JS</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Jiangsu, China</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>8</v>
+      </c>
+      <c r="O30" t="n">
+        <v>8</v>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>country:CN-JS:national</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Human Clonorchis sinensis infection. The Chinese source category 肝吸虫病 denotes clonorchiasis, not all trematode infections.</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP30" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ30" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AT30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV30" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA30" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB30" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+        </is>
+      </c>
+      <c r="BC30" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>clonorchiasis</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>CN-JX</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Jiangxi, China</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>15</v>
+      </c>
+      <c r="O31" t="n">
+        <v>15</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP31" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ31" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AT31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV31" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA31" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB31" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.jxcdc.cn/</t>
+        </is>
+      </c>
+      <c r="BC31" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>clonorchiasis</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>CN-JX</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Jiangxi, China</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>15</v>
+      </c>
+      <c r="O32" t="n">
+        <v>15</v>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>country:CN-JX:national</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Human Clonorchis sinensis infection. The Chinese source category 肝吸虫病 denotes clonorchiasis, not all trematode infections.</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN32" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AT32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV32" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA32" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB32" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.jxcdc.cn/</t>
+        </is>
+      </c>
+      <c r="BC32" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>clonorchiasis</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>CN-SH</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Shanghai, China</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>10</v>
+      </c>
+      <c r="O33" t="n">
+        <v>10</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ33" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AT33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV33" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA33" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB33" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+        </is>
+      </c>
+      <c r="BC33" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>clonorchiasis</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>CN-SH</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Shanghai, China</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>10</v>
+      </c>
+      <c r="O34" t="n">
+        <v>10</v>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>country:CN-SH:national</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Human Clonorchis sinensis infection. The Chinese source category 肝吸虫病 denotes clonorchiasis, not all trematode infections.</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN34" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP34" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AT34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV34" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA34" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB34" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+        </is>
+      </c>
+      <c r="BC34" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>clonorchiasis</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>CN-SX</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Shanxi, China</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP35" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ35" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AT35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV35" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA35" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB35" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.shanxi.gov.cn/zfxxgk/fdzdgknr/yqfb/</t>
+        </is>
+      </c>
+      <c r="BC35" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>clonorchiasis</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>CN-SX</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Shanxi, China</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>country:CN-SX:national</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Human Clonorchis sinensis infection. The Chinese source category 肝吸虫病 denotes clonorchiasis, not all trematode infections.</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN36" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP36" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ36" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AT36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV36" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA36" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB36" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.shanxi.gov.cn/zfxxgk/fdzdgknr/yqfb/</t>
+        </is>
+      </c>
+      <c r="BC36" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>clonorchiasis</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>12759</v>
+      </c>
+      <c r="O37" t="n">
+        <v>12759</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.9030273039138147</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP37" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr"/>
+      <c r="AT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV37" t="inlineStr">
+        <is>
+          <t>cdc_weekly</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>China CDC Weekly</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>cdc_weekly; nhc; pubmed</t>
+        </is>
+      </c>
+      <c r="BA37" t="inlineStr">
+        <is>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+        </is>
+      </c>
+      <c r="BB37" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+        </is>
+      </c>
+      <c r="BC37" t="inlineStr">
+        <is>
+          <t>web; web; web</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>clonorchiasis</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>CN-GX</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Guangxi, China</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>3538</v>
+      </c>
+      <c r="O38" t="n">
+        <v>3538</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP38" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ38" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS38" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AT38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV38" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA38" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB38" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
+        </is>
+      </c>
+      <c r="BC38" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>clonorchiasis</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>CN-GX</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Guangxi, China</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>3538</v>
+      </c>
+      <c r="O39" t="n">
+        <v>3538</v>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>country:CN-GX:national</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Human Clonorchis sinensis infection. The Chinese source category 肝吸虫病 denotes clonorchiasis, not all trematode infections.</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP39" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ39" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AT39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV39" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA39" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB39" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
+        </is>
+      </c>
+      <c r="BC39" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>clonorchiasis</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>CN-JS</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Jiangsu, China</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>3</v>
+      </c>
+      <c r="O40" t="n">
+        <v>3</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP40" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ40" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AT40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV40" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA40" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB40" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+        </is>
+      </c>
+      <c r="BC40" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>clonorchiasis</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>CN-JS</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Jiangsu, China</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>3</v>
+      </c>
+      <c r="O41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>country:CN-JS:national</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Human Clonorchis sinensis infection. The Chinese source category 肝吸虫病 denotes clonorchiasis, not all trematode infections.</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN41" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP41" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ41" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AT41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV41" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA41" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB41" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+        </is>
+      </c>
+      <c r="BC41" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>clonorchiasis</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>CN-SH</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Shanghai, China</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>11</v>
+      </c>
+      <c r="O42" t="n">
+        <v>11</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP42" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ42" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS42" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AT42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV42" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA42" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB42" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+        </is>
+      </c>
+      <c r="BC42" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>clonorchiasis</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>CN-SH</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Shanghai, China</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>11</v>
+      </c>
+      <c r="O43" t="n">
+        <v>11</v>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>country:CN-SH:national</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Human Clonorchis sinensis infection. The Chinese source category 肝吸虫病 denotes clonorchiasis, not all trematode infections.</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN43" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP43" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ43" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS43" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AT43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV43" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA43" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB43" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+        </is>
+      </c>
+      <c r="BC43" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>clonorchiasis</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>CN-SX</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Shanxi, China</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP44" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ44" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AT44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV44" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA44" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB44" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.shanxi.gov.cn/zfxxgk/fdzdgknr/yqfb/</t>
+        </is>
+      </c>
+      <c r="BC44" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>clonorchiasis</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>CN-SX</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Shanxi, China</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>country:CN-SX:national</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Human Clonorchis sinensis infection. The Chinese source category 肝吸虫病 denotes clonorchiasis, not all trematode infections.</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN45" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP45" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ45" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AT45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV45" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA45" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB45" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.shanxi.gov.cn/zfxxgk/fdzdgknr/yqfb/</t>
+        </is>
+      </c>
+      <c r="BC45" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>clonorchiasis</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>CN-GX</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Guangxi, China</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>3527</v>
+      </c>
+      <c r="O46" t="n">
+        <v>3527</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP46" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ46" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AT46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV46" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA46" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB46" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
+        </is>
+      </c>
+      <c r="BC46" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>clonorchiasis</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>CN-GX</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Guangxi, China</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Clonorchiasis</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>3527</v>
+      </c>
+      <c r="O47" t="n">
+        <v>3527</v>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>肝吸虫病</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>country:CN-GX:national</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Human Clonorchis sinensis infection. The Chinese source category 肝吸虫病 denotes clonorchiasis, not all trematode infections.</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN47" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP47" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ47" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_CLONORCHIASIS</t>
+        </is>
+      </c>
+      <c r="AT47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV47" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA47" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB47" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
+        </is>
+      </c>
+      <c r="BC47" t="inlineStr">
         <is>
           <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
@@ -4680,7 +9360,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -4763,7 +9443,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10">
@@ -4773,7 +9453,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11">
@@ -4793,7 +9473,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
@@ -4825,7 +9505,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>85156</v>
+        <v>101758</v>
       </c>
     </row>
     <row r="16">
